--- a/PMS_Report_DPR-385_Period_2026-03-28_to_2026-07-26.xlsx
+++ b/PMS_Report_DPR-385_Period_2026-03-28_to_2026-07-26.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,12 +41,6 @@
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="000000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="3">
@@ -75,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -86,7 +80,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -527,7 +520,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26 16:51</t>
+          <t>2026-07-26 17:22</t>
         </is>
       </c>
     </row>
@@ -644,7 +637,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -668,7 +661,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -734,7 +727,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -776,7 +769,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -842,18 +835,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="23" customWidth="1" min="4" max="4"/>
-    <col width="43" customWidth="1" min="5" max="5"/>
-    <col width="60" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -903,57 +896,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>BfArM (Germania)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BfArM-FSN-DICOM VIEWER-2024</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>15/02/2024</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>BfArM Monitored Firm</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Medical Device / Software (DICOM viewer)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Field Safety Notice riguardante la sicurezza per ricerche su 'DICOM viewer'</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Field Safety Notice (Drisiko/BfArM)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>https://www.bfarm.de/EN/MedicalDevices/Risks/FieldSafetyNotices/_node.html?query=DICOM viewer</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I2" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>